--- a/app/data/Metadata_Access.xlsx
+++ b/app/data/Metadata_Access.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Public troubleshooting &amp; user manual graph</t>
+          <t>Troubleshooting, service catalogue, and business metric definitions.</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Public troubleshooting &amp; user manual graph</t>
+          <t>Troubleshooting, service catalogue, and business metric definitions.</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Full access to edit knowledge base graph</t>
+          <t>Full knowledge graph administration.</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Operational live telemetry &amp; grid pressure metrics</t>
+          <t>Operational telemetry and network readings.</t>
         </is>
       </c>
     </row>
@@ -544,29 +544,95 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Full access to live metrics telemetry</t>
+          <t>Full telemetry access.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Business_Operations</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Employee</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Read-Only</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Aggregated commercial, service, and sales-performance records.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Business_Operations</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Read-Write</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Full operational dataset access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Metadata_Access</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Full-Access</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Access-policy administration and audit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>System_Logs</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Admin</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Full-Access</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Sensitive infrastructure system logs</t>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sensitive infrastructure system logs.</t>
         </is>
       </c>
     </row>
